--- a/fixtures/files/workbuster_deltagare_MBR.xlsx
+++ b/fixtures/files/workbuster_deltagare_MBR.xlsx
@@ -467,7 +467,7 @@
         <v>Arvid Larsson</v>
       </c>
       <c r="C5" t="str">
-        <v>810929-4762</v>
+        <v>810929-9894</v>
       </c>
       <c r="D5" t="str">
         <v>Stöd och matchning</v>
@@ -490,7 +490,7 @@
         <v>Gustav Lindqvist</v>
       </c>
       <c r="C6" t="str">
-        <v>680602-8053</v>
+        <v>680602-9960</v>
       </c>
       <c r="D6" t="str">
         <v>KROM</v>
@@ -510,7 +510,7 @@
         <v>Ali Wallin</v>
       </c>
       <c r="C7" t="str">
-        <v>040402-9068</v>
+        <v>040402-9985</v>
       </c>
       <c r="D7" t="str">
         <v>Stöd och matchning</v>
@@ -539,7 +539,7 @@
         <v>Klara Engström</v>
       </c>
       <c r="C8" t="str">
-        <v>870321-6419</v>
+        <v>870321-9926</v>
       </c>
       <c r="D8" t="str">
         <v>KVL</v>
@@ -568,7 +568,7 @@
         <v>Fatima Lindström</v>
       </c>
       <c r="C9" t="str">
-        <v>951209-0094</v>
+        <v>951209-9806</v>
       </c>
       <c r="D9" t="str">
         <v>Stöd och matchning</v>
@@ -588,7 +588,7 @@
         <v>Rania Larsson</v>
       </c>
       <c r="C10" t="str">
-        <v>781120-4598</v>
+        <v>781120-9894</v>
       </c>
       <c r="D10" t="str">
         <v>Stöd och matchning</v>
@@ -617,7 +617,7 @@
         <v>Yusuf Mattsson</v>
       </c>
       <c r="C11" t="str">
-        <v>670116-2080</v>
+        <v>670116-9846</v>
       </c>
       <c r="D11" t="str">
         <v>Stöd och matchning</v>
@@ -640,7 +640,7 @@
         <v>Mohammed Abdullahi</v>
       </c>
       <c r="C12" t="str">
-        <v>890929-9987</v>
+        <v>890929-9995</v>
       </c>
       <c r="D12" t="str">
         <v>ROM2</v>
@@ -660,7 +660,7 @@
         <v>Elin Karlsson</v>
       </c>
       <c r="C13" t="str">
-        <v>880815-5322</v>
+        <v>880815-9902</v>
       </c>
       <c r="D13" t="str">
         <v>Stöd och matchning</v>
@@ -680,7 +680,7 @@
         <v>Vera Sjöberg</v>
       </c>
       <c r="C14" t="str">
-        <v>730406-0580</v>
+        <v>730406-9813</v>
       </c>
       <c r="D14" t="str">
         <v>ROM2</v>
@@ -709,7 +709,7 @@
         <v>Arvid Hussein</v>
       </c>
       <c r="C15" t="str">
-        <v>650526-1096</v>
+        <v>650526-9826</v>
       </c>
       <c r="D15" t="str">
         <v>KROM</v>
@@ -729,7 +729,7 @@
         <v>Mohammed Hussein</v>
       </c>
       <c r="C16" t="str">
-        <v>980929-3492</v>
+        <v>980929-9861</v>
       </c>
       <c r="D16" t="str">
         <v>KROM</v>
@@ -752,7 +752,7 @@
         <v>Arvid Eklund</v>
       </c>
       <c r="C17" t="str">
-        <v>630811-1852</v>
+        <v>630811-9830</v>
       </c>
       <c r="D17" t="str">
         <v>ROM2</v>
@@ -772,7 +772,7 @@
         <v>Freja Öberg</v>
       </c>
       <c r="C18" t="str">
-        <v>710414-3610</v>
+        <v>710414-9872</v>
       </c>
       <c r="D18" t="str">
         <v>KROM</v>
@@ -801,7 +801,7 @@
         <v>Anna Pettersson</v>
       </c>
       <c r="C19" t="str">
-        <v>800601-7027</v>
+        <v>800601-9940</v>
       </c>
       <c r="D19" t="str">
         <v>Stöd och matchning</v>
@@ -821,7 +821,7 @@
         <v>Gustav Jansson</v>
       </c>
       <c r="C20" t="str">
-        <v>870106-7749</v>
+        <v>870106-9950</v>
       </c>
       <c r="D20" t="str">
         <v>ROM2</v>
@@ -841,7 +841,7 @@
         <v>Rania Sandberg</v>
       </c>
       <c r="C21" t="str">
-        <v>770506-1450</v>
+        <v>770506-9826</v>
       </c>
       <c r="D21" t="str">
         <v>Stöd och matchning</v>
@@ -870,7 +870,7 @@
         <v>Abdi Nilsson</v>
       </c>
       <c r="C22" t="str">
-        <v>780127-9022</v>
+        <v>780127-9980</v>
       </c>
       <c r="D22" t="str">
         <v>KVL</v>
@@ -893,7 +893,7 @@
         <v>Rania Danielsson</v>
       </c>
       <c r="C23" t="str">
-        <v>861210-4631</v>
+        <v>861210-9895</v>
       </c>
       <c r="D23" t="str">
         <v>ROM2</v>
@@ -922,7 +922,7 @@
         <v>Sofia Bergström</v>
       </c>
       <c r="C24" t="str">
-        <v>010419-3636</v>
+        <v>010419-9872</v>
       </c>
       <c r="D24" t="str">
         <v>KROM</v>
@@ -945,7 +945,7 @@
         <v>Kerim Abdullahi</v>
       </c>
       <c r="C25" t="str">
-        <v>751217-9867</v>
+        <v>751217-9990</v>
       </c>
       <c r="D25" t="str">
         <v>Stöd och matchning</v>
@@ -974,7 +974,7 @@
         <v>Filip Hassan</v>
       </c>
       <c r="C26" t="str">
-        <v>930324-0981</v>
+        <v>930324-9818</v>
       </c>
       <c r="D26" t="str">
         <v>Stöd och matchning</v>
@@ -994,7 +994,7 @@
         <v>Gustav Kaya</v>
       </c>
       <c r="C27" t="str">
-        <v>700917-5410</v>
+        <v>700917-9909</v>
       </c>
       <c r="D27" t="str">
         <v>Stöd och matchning</v>
@@ -1017,7 +1017,7 @@
         <v>Gustav Kaya</v>
       </c>
       <c r="C28" t="str">
-        <v>700917-5410</v>
+        <v>700917-9909</v>
       </c>
       <c r="D28" t="str">
         <v>Stöd och matchning</v>
@@ -1040,7 +1040,7 @@
         <v>Mariam Nordin</v>
       </c>
       <c r="C29" t="str">
-        <v>671028-7571</v>
+        <v>671028-9957</v>
       </c>
       <c r="D29" t="str">
         <v>KVL</v>
@@ -1069,7 +1069,7 @@
         <v>Jonas Nyström</v>
       </c>
       <c r="C30" t="str">
-        <v>790119-0400</v>
+        <v>790119-9807</v>
       </c>
       <c r="D30" t="str">
         <v>Stöd och matchning</v>
@@ -1098,7 +1098,7 @@
         <v>Selma Lindberg</v>
       </c>
       <c r="C31" t="str">
-        <v>640203-7185</v>
+        <v>640203-9942</v>
       </c>
       <c r="D31" t="str">
         <v>KROM</v>
@@ -1118,7 +1118,7 @@
         <v>Kerim Nordin</v>
       </c>
       <c r="C32" t="str">
-        <v>691222-5783</v>
+        <v>691222-9918</v>
       </c>
       <c r="D32" t="str">
         <v>Stöd och matchning</v>
@@ -1147,7 +1147,7 @@
         <v>Wilma Mohamed</v>
       </c>
       <c r="C33" t="str">
-        <v>900311-5301</v>
+        <v>900311-9907</v>
       </c>
       <c r="D33" t="str">
         <v>Stöd och matchning</v>
@@ -1170,7 +1170,7 @@
         <v>Jonas Mohamed</v>
       </c>
       <c r="C34" t="str">
-        <v>940128-0392</v>
+        <v>940128-9807</v>
       </c>
       <c r="D34" t="str">
         <v>KROM</v>
@@ -1190,7 +1190,7 @@
         <v>Lina Nilsson</v>
       </c>
       <c r="C35" t="str">
-        <v>640703-7479</v>
+        <v>640703-9947</v>
       </c>
       <c r="D35" t="str">
         <v>KROM</v>
@@ -1213,7 +1213,7 @@
         <v>Anna Karlsson</v>
       </c>
       <c r="C36" t="str">
-        <v>961227-3590</v>
+        <v>961227-9878</v>
       </c>
       <c r="D36" t="str">
         <v>KROM</v>
@@ -1242,7 +1242,7 @@
         <v>Alva Jakobsson</v>
       </c>
       <c r="C37" t="str">
-        <v>971205-6853</v>
+        <v>971205-9931</v>
       </c>
       <c r="D37" t="str">
         <v>Stöd och matchning</v>
@@ -1271,7 +1271,7 @@
         <v>Mariam Axelsson</v>
       </c>
       <c r="C38" t="str">
-        <v>840214-3682</v>
+        <v>840214-9879</v>
       </c>
       <c r="D38" t="str">
         <v>ROM2</v>
@@ -1300,7 +1300,7 @@
         <v>Elin Gustafsson</v>
       </c>
       <c r="C39" t="str">
-        <v>700410-3276</v>
+        <v>700410-9869</v>
       </c>
       <c r="D39" t="str">
         <v>Stöd och matchning</v>
@@ -1329,7 +1329,7 @@
         <v>Isak Lindberg</v>
       </c>
       <c r="C40" t="str">
-        <v>630105-6765</v>
+        <v>630105-9934</v>
       </c>
       <c r="D40" t="str">
         <v>KVL</v>
@@ -1352,7 +1352,7 @@
         <v>Lina Jonsson</v>
       </c>
       <c r="C41" t="str">
-        <v>030910-2242</v>
+        <v>030910-9841</v>
       </c>
       <c r="D41" t="str">
         <v>KROM</v>
@@ -1372,7 +1372,7 @@
         <v>Hugo Holm</v>
       </c>
       <c r="C42" t="str">
-        <v>020619-8293</v>
+        <v>020619-9960</v>
       </c>
       <c r="D42" t="str">
         <v>KROM</v>
@@ -1395,7 +1395,7 @@
         <v>Freja Söderberg</v>
       </c>
       <c r="C43" t="str">
-        <v>640628-4973</v>
+        <v>640628-9899</v>
       </c>
       <c r="D43" t="str">
         <v>KROM</v>
@@ -1424,7 +1424,7 @@
         <v>Ebba Jönsson</v>
       </c>
       <c r="C44" t="str">
-        <v>920726-4384</v>
+        <v>920726-9888</v>
       </c>
       <c r="D44" t="str">
         <v>Stöd och matchning</v>
@@ -1447,7 +1447,7 @@
         <v>Hugo Öberg</v>
       </c>
       <c r="C45" t="str">
-        <v>020505-0875</v>
+        <v>020505-9819</v>
       </c>
       <c r="D45" t="str">
         <v>ROM2</v>
@@ -1467,7 +1467,7 @@
         <v>Wilma Mattsson</v>
       </c>
       <c r="C46" t="str">
-        <v>681214-2690</v>
+        <v>681214-9851</v>
       </c>
       <c r="D46" t="str">
         <v>KROM</v>
@@ -1490,7 +1490,7 @@
         <v>Yusuf Jakobsson</v>
       </c>
       <c r="C47" t="str">
-        <v>680628-4334</v>
+        <v>680628-9887</v>
       </c>
       <c r="D47" t="str">
         <v>KROM</v>
@@ -1510,7 +1510,7 @@
         <v>Amina Holm</v>
       </c>
       <c r="C48" t="str">
-        <v>880328-4960</v>
+        <v>880328-9894</v>
       </c>
       <c r="D48" t="str">
         <v>KROM</v>
@@ -1533,7 +1533,7 @@
         <v>Kerim Jonsson</v>
       </c>
       <c r="C49" t="str">
-        <v>910826-7023</v>
+        <v>910826-9946</v>
       </c>
       <c r="D49" t="str">
         <v>ROM2</v>
@@ -1556,7 +1556,7 @@
         <v>Ludvig Berg</v>
       </c>
       <c r="C50" t="str">
-        <v>810809-8743</v>
+        <v>810809-9972</v>
       </c>
       <c r="D50" t="str">
         <v>ROM2</v>
@@ -1585,7 +1585,7 @@
         <v>Adam Mattsson</v>
       </c>
       <c r="C51" t="str">
-        <v>690623-6622</v>
+        <v>690623-9931</v>
       </c>
       <c r="D51" t="str">
         <v>Stöd och matchning</v>
@@ -1605,7 +1605,7 @@
         <v>Freja Olsson</v>
       </c>
       <c r="C52" t="str">
-        <v>780402-6438</v>
+        <v>780402-9929</v>
       </c>
       <c r="D52" t="str">
         <v>KROM</v>
@@ -1634,7 +1634,7 @@
         <v>Hanna Jonsson</v>
       </c>
       <c r="C53" t="str">
-        <v>850920-4452</v>
+        <v>850920-9881</v>
       </c>
       <c r="D53" t="str">
         <v>KROM</v>
@@ -1657,7 +1657,7 @@
         <v>Lina Persson</v>
       </c>
       <c r="C54" t="str">
-        <v>681006-5786</v>
+        <v>681006-9911</v>
       </c>
       <c r="D54" t="str">
         <v>KROM</v>
@@ -1686,7 +1686,7 @@
         <v>Sofia Bengtsson</v>
       </c>
       <c r="C55" t="str">
-        <v>040409-9293</v>
+        <v>040409-9988</v>
       </c>
       <c r="D55" t="str">
         <v>Stöd och matchning</v>
@@ -1715,7 +1715,7 @@
         <v>Amina Magnusson</v>
       </c>
       <c r="C56" t="str">
-        <v>860510-5009</v>
+        <v>860510-9894</v>
       </c>
       <c r="D56" t="str">
         <v>Stöd och matchning</v>
@@ -1738,7 +1738,7 @@
         <v>Hassan Bengtsson</v>
       </c>
       <c r="C57" t="str">
-        <v>050602-1021</v>
+        <v>050602-9826</v>
       </c>
       <c r="D57" t="str">
         <v>ROM2</v>
@@ -1761,7 +1761,7 @@
         <v>Nadia Hassan</v>
       </c>
       <c r="C58" t="str">
-        <v>911112-5051</v>
+        <v>911112-9905</v>
       </c>
       <c r="D58" t="str">
         <v>ROM2</v>
@@ -1790,7 +1790,7 @@
         <v>Noor Bengtsson</v>
       </c>
       <c r="C59" t="str">
-        <v>831003-8008</v>
+        <v>831003-9964</v>
       </c>
       <c r="D59" t="str">
         <v>KROM</v>
@@ -1810,7 +1810,7 @@
         <v>Agnes Eklund</v>
       </c>
       <c r="C60" t="str">
-        <v>641111-6905</v>
+        <v>641111-9933</v>
       </c>
       <c r="D60" t="str">
         <v>ROM2</v>
@@ -1833,7 +1833,7 @@
         <v>Hassan Nyström</v>
       </c>
       <c r="C61" t="str">
-        <v>981127-1783</v>
+        <v>981127-9836</v>
       </c>
       <c r="D61" t="str">
         <v>ROM2</v>
@@ -1856,7 +1856,7 @@
         <v>Mariam Holm</v>
       </c>
       <c r="C62" t="str">
-        <v>651001-1965</v>
+        <v>651001-9836</v>
       </c>
       <c r="D62" t="str">
         <v>Stöd och matchning</v>
@@ -1885,7 +1885,7 @@
         <v>Filip Olsson</v>
       </c>
       <c r="C63" t="str">
-        <v>890811-2132</v>
+        <v>890811-9848</v>
       </c>
       <c r="D63" t="str">
         <v>Stöd och matchning</v>
@@ -1905,7 +1905,7 @@
         <v>Emil Pettersson</v>
       </c>
       <c r="C64" t="str">
-        <v>880626-8119</v>
+        <v>880626-9968</v>
       </c>
       <c r="D64" t="str">
         <v>Stöd och matchning</v>
@@ -1934,7 +1934,7 @@
         <v>Viktor Engström</v>
       </c>
       <c r="C65" t="str">
-        <v>840216-4118</v>
+        <v>840216-9885</v>
       </c>
       <c r="D65" t="str">
         <v>ROM2</v>
@@ -1963,7 +1963,7 @@
         <v>Ebba Bengtsson</v>
       </c>
       <c r="C66" t="str">
-        <v>710917-8280</v>
+        <v>710917-9965</v>
       </c>
       <c r="D66" t="str">
         <v>ROM2</v>
@@ -1992,7 +1992,7 @@
         <v>Ida Söderberg</v>
       </c>
       <c r="C67" t="str">
-        <v>680115-1678</v>
+        <v>680115-9838</v>
       </c>
       <c r="D67" t="str">
         <v>KROM</v>
@@ -2015,7 +2015,7 @@
         <v>Oskar Kaya</v>
       </c>
       <c r="C68" t="str">
-        <v>660527-8628</v>
+        <v>660527-9972</v>
       </c>
       <c r="D68" t="str">
         <v>Stöd och matchning</v>
@@ -2038,7 +2038,7 @@
         <v>Ludvig Hussein</v>
       </c>
       <c r="C69" t="str">
-        <v>680624-5798</v>
+        <v>680624-9915</v>
       </c>
       <c r="D69" t="str">
         <v>Stöd och matchning</v>
@@ -2058,7 +2058,7 @@
         <v>Ahmed Hussein</v>
       </c>
       <c r="C70" t="str">
-        <v>741218-2102</v>
+        <v>741218-9842</v>
       </c>
       <c r="D70" t="str">
         <v>KROM</v>
@@ -2078,7 +2078,7 @@
         <v>Isak Åberg</v>
       </c>
       <c r="C71" t="str">
-        <v>810527-7464</v>
+        <v>810527-9940</v>
       </c>
       <c r="D71" t="str">
         <v>Stöd och matchning</v>
@@ -2107,7 +2107,7 @@
         <v>Oskar Lindqvist</v>
       </c>
       <c r="C72" t="str">
-        <v>010606-5527</v>
+        <v>010606-9917</v>
       </c>
       <c r="D72" t="str">
         <v>KROM</v>
@@ -2136,7 +2136,7 @@
         <v>Zainab Bengtsson</v>
       </c>
       <c r="C73" t="str">
-        <v>900807-5344</v>
+        <v>900807-9908</v>
       </c>
       <c r="D73" t="str">
         <v>Stöd och matchning</v>
@@ -2159,7 +2159,7 @@
         <v>Ali Söderberg</v>
       </c>
       <c r="C74" t="str">
-        <v>860319-4849</v>
+        <v>860319-9897</v>
       </c>
       <c r="D74" t="str">
         <v>Stöd och matchning</v>
@@ -2188,7 +2188,7 @@
         <v>Viktor Magnusson</v>
       </c>
       <c r="C75" t="str">
-        <v>820105-3207</v>
+        <v>820105-9865</v>
       </c>
       <c r="D75" t="str">
         <v>KROM</v>
@@ -2211,7 +2211,7 @@
         <v>Aisha Kaya</v>
       </c>
       <c r="C76" t="str">
-        <v>920314-4283</v>
+        <v>920314-9886</v>
       </c>
       <c r="D76" t="str">
         <v>Stöd och matchning</v>
@@ -2240,7 +2240,7 @@
         <v>Hanna Persson</v>
       </c>
       <c r="C77" t="str">
-        <v>870725-9845</v>
+        <v>870725-9993</v>
       </c>
       <c r="D77" t="str">
         <v>ROM2</v>
@@ -2263,7 +2263,7 @@
         <v>Hugo Hansson</v>
       </c>
       <c r="C78" t="str">
-        <v>650325-9720</v>
+        <v>650325-9993</v>
       </c>
       <c r="D78" t="str">
         <v>ROM2</v>
@@ -2283,7 +2283,7 @@
         <v>Viktor Johansson</v>
       </c>
       <c r="C79" t="str">
-        <v>691207-9594</v>
+        <v>691207-9990</v>
       </c>
       <c r="D79" t="str">
         <v>KVL</v>
@@ -2312,7 +2312,7 @@
         <v>Sofia Forsberg</v>
       </c>
       <c r="C80" t="str">
-        <v>701130-9957</v>
+        <v>701130-9999</v>
       </c>
       <c r="D80" t="str">
         <v>Stöd och matchning</v>
@@ -2341,7 +2341,7 @@
         <v>Ahmed Lundin</v>
       </c>
       <c r="C81" t="str">
-        <v>901203-2943</v>
+        <v>901203-9856</v>
       </c>
       <c r="D81" t="str">
         <v>KROM</v>
@@ -2364,7 +2364,7 @@
         <v>Sara Fransson</v>
       </c>
       <c r="C82" t="str">
-        <v>620717-8853</v>
+        <v>620717-9976</v>
       </c>
       <c r="D82" t="str">
         <v>KROM</v>
@@ -2390,7 +2390,7 @@
         <v>Maja Magnusson</v>
       </c>
       <c r="C83" t="str">
-        <v>731202-0816</v>
+        <v>731202-9817</v>
       </c>
       <c r="D83" t="str">
         <v>Stöd och matchning</v>
@@ -2410,7 +2410,7 @@
         <v>Jakob Bergström</v>
       </c>
       <c r="C84" t="str">
-        <v>840401-4626</v>
+        <v>840401-9898</v>
       </c>
       <c r="D84" t="str">
         <v>Stöd och matchning</v>
@@ -2430,7 +2430,7 @@
         <v>Aisha Hassan</v>
       </c>
       <c r="C85" t="str">
-        <v>810120-2755</v>
+        <v>810120-9859</v>
       </c>
       <c r="D85" t="str">
         <v>Stöd och matchning</v>
@@ -2453,7 +2453,7 @@
         <v>Ida Persson</v>
       </c>
       <c r="C86" t="str">
-        <v>810628-8700</v>
+        <v>810628-9971</v>
       </c>
       <c r="D86" t="str">
         <v>KROM</v>
@@ -2482,7 +2482,7 @@
         <v>Sara Larsson</v>
       </c>
       <c r="C87" t="str">
-        <v>940424-0773</v>
+        <v>940424-9816</v>
       </c>
       <c r="D87" t="str">
         <v>Stöd och matchning</v>
@@ -2511,7 +2511,7 @@
         <v>Ludvig Ahmed</v>
       </c>
       <c r="C88" t="str">
-        <v>840615-1855</v>
+        <v>840615-9833</v>
       </c>
       <c r="D88" t="str">
         <v>Stöd och matchning</v>
@@ -2534,7 +2534,7 @@
         <v>Anna Nilsson</v>
       </c>
       <c r="C89" t="str">
-        <v>701224-0300</v>
+        <v>701224-9806</v>
       </c>
       <c r="D89" t="str">
         <v>KROM</v>
@@ -2554,7 +2554,7 @@
         <v>Sara Bergström</v>
       </c>
       <c r="C90" t="str">
-        <v>970826-4354</v>
+        <v>970826-9882</v>
       </c>
       <c r="D90" t="str">
         <v>KROM</v>
@@ -2577,7 +2577,7 @@
         <v>Rania Wallin</v>
       </c>
       <c r="C91" t="str">
-        <v>700205-2137</v>
+        <v>700205-9843</v>
       </c>
       <c r="D91" t="str">
         <v>KROM</v>
@@ -2606,7 +2606,7 @@
         <v>Ali Gustafsson</v>
       </c>
       <c r="C92" t="str">
-        <v>670930-9642</v>
+        <v>670930-9998</v>
       </c>
       <c r="D92" t="str">
         <v>ROM2</v>
@@ -2629,7 +2629,7 @@
         <v>Abdi Ahmed</v>
       </c>
       <c r="C93" t="str">
-        <v>030322-1626</v>
+        <v>030322-9835</v>
       </c>
       <c r="D93" t="str">
         <v>KROM</v>
@@ -2658,7 +2658,7 @@
         <v>Adam Jönsson</v>
       </c>
       <c r="C94" t="str">
-        <v>841208-2649</v>
+        <v>841208-9859</v>
       </c>
       <c r="D94" t="str">
         <v>ROM2</v>
@@ -2681,7 +2681,7 @@
         <v>Saga Lindström</v>
       </c>
       <c r="C95" t="str">
-        <v>870320-6592</v>
+        <v>870320-9935</v>
       </c>
       <c r="D95" t="str">
         <v>Stöd och matchning</v>
@@ -2710,7 +2710,7 @@
         <v>Elias Ström</v>
       </c>
       <c r="C96" t="str">
-        <v>010514-4521</v>
+        <v>010514-9892</v>
       </c>
       <c r="D96" t="str">
         <v>Stöd och matchning</v>
@@ -2730,7 +2730,7 @@
         <v>Ali Hussein</v>
       </c>
       <c r="C97" t="str">
-        <v>950908-9273</v>
+        <v>950908-9984</v>
       </c>
       <c r="D97" t="str">
         <v>Stöd och matchning</v>
@@ -2753,7 +2753,7 @@
         <v>Alva Jansson</v>
       </c>
       <c r="C98" t="str">
-        <v>910807-8446</v>
+        <v>910807-9964</v>
       </c>
       <c r="D98" t="str">
         <v>Stöd och matchning</v>
@@ -2776,7 +2776,7 @@
         <v>Hugo Johansson</v>
       </c>
       <c r="C99" t="str">
-        <v>881124-7249</v>
+        <v>881124-9948</v>
       </c>
       <c r="D99" t="str">
         <v>KVL</v>
@@ -2799,7 +2799,7 @@
         <v>Sofia Berg</v>
       </c>
       <c r="C100" t="str">
-        <v>680912-1392</v>
+        <v>680912-9825</v>
       </c>
       <c r="D100" t="str">
         <v>Stöd och matchning</v>
@@ -2828,7 +2828,7 @@
         <v>Nadia Engström</v>
       </c>
       <c r="C101" t="str">
-        <v>900506-1594</v>
+        <v>900506-9837</v>
       </c>
       <c r="D101" t="str">
         <v>Stöd och matchning</v>
@@ -2857,7 +2857,7 @@
         <v>Ludvig Gustafsson</v>
       </c>
       <c r="C102" t="str">
-        <v>961203-3408</v>
+        <v>961203-9868</v>
       </c>
       <c r="D102" t="str">
         <v>KROM</v>
@@ -2886,7 +2886,7 @@
         <v>Ibrahim Lindqvist</v>
       </c>
       <c r="C103" t="str">
-        <v>690606-7142</v>
+        <v>690606-9940</v>
       </c>
       <c r="D103" t="str">
         <v>Stöd och matchning</v>
@@ -2909,7 +2909,7 @@
         <v>Aisha Persson</v>
       </c>
       <c r="C104" t="str">
-        <v>680207-2071</v>
+        <v>680207-9845</v>
       </c>
       <c r="D104" t="str">
         <v>KROM</v>
@@ -2932,7 +2932,7 @@
         <v>Hugo Ström</v>
       </c>
       <c r="C105" t="str">
-        <v>731120-2076</v>
+        <v>731120-9840</v>
       </c>
       <c r="D105" t="str">
         <v>KROM</v>
@@ -2961,7 +2961,7 @@
         <v>Hugo Hussein</v>
       </c>
       <c r="C106" t="str">
-        <v>701218-7584</v>
+        <v>701218-9952</v>
       </c>
       <c r="D106" t="str">
         <v>Stöd och matchning</v>
@@ -2990,7 +2990,7 @@
         <v>Lucas Svensson</v>
       </c>
       <c r="C107" t="str">
-        <v>951028-9680</v>
+        <v>951028-9995</v>
       </c>
       <c r="D107" t="str">
         <v>KROM</v>
@@ -3019,7 +3019,7 @@
         <v>Freja Holm</v>
       </c>
       <c r="C108" t="str">
-        <v>941213-7201</v>
+        <v>941213-9942</v>
       </c>
       <c r="D108" t="str">
         <v>KVL</v>
@@ -3042,7 +3042,7 @@
         <v>Ibrahim Magnusson</v>
       </c>
       <c r="C109" t="str">
-        <v>820419-1053</v>
+        <v>820419-9825</v>
       </c>
       <c r="D109" t="str">
         <v>KROM</v>
@@ -3071,7 +3071,7 @@
         <v>Lina Wallin</v>
       </c>
       <c r="C110" t="str">
-        <v>020902-2276</v>
+        <v>020902-9842</v>
       </c>
       <c r="D110" t="str">
         <v>KROM</v>
@@ -3094,7 +3094,7 @@
         <v>Jakob Larsson</v>
       </c>
       <c r="C111" t="str">
-        <v>710513-9591</v>
+        <v>710513-9997</v>
       </c>
       <c r="D111" t="str">
         <v>Stöd och matchning</v>
@@ -3117,7 +3117,7 @@
         <v>Sofia Fransson</v>
       </c>
       <c r="C112" t="str">
-        <v>750813-0700</v>
+        <v>750813-9818</v>
       </c>
       <c r="D112" t="str">
         <v>ROM2</v>
@@ -3146,7 +3146,7 @@
         <v>Rania Engström</v>
       </c>
       <c r="C113" t="str">
-        <v>620611-5443</v>
+        <v>620611-9908</v>
       </c>
       <c r="D113" t="str">
         <v>Stöd och matchning</v>
@@ -3175,7 +3175,7 @@
         <v>Selma Jönsson</v>
       </c>
       <c r="C114" t="str">
-        <v>030505-4967</v>
+        <v>030505-9891</v>
       </c>
       <c r="D114" t="str">
         <v>Stöd och matchning</v>
@@ -3198,7 +3198,7 @@
         <v>Hassan Svensson</v>
       </c>
       <c r="C115" t="str">
-        <v>640320-8314</v>
+        <v>640320-9965</v>
       </c>
       <c r="D115" t="str">
         <v>Stöd och matchning</v>
@@ -3218,7 +3218,7 @@
         <v>Vera Pettersson</v>
       </c>
       <c r="C116" t="str">
-        <v>040626-6627</v>
+        <v>040626-9936</v>
       </c>
       <c r="D116" t="str">
         <v>KROM</v>
@@ -3238,7 +3238,7 @@
         <v>Hugo Lundin</v>
       </c>
       <c r="C117" t="str">
-        <v>751115-1610</v>
+        <v>751115-9837</v>
       </c>
       <c r="D117" t="str">
         <v>Stöd och matchning</v>
@@ -3267,7 +3267,7 @@
         <v>Aisha Söderberg</v>
       </c>
       <c r="C118" t="str">
-        <v>010301-6465</v>
+        <v>010301-9923</v>
       </c>
       <c r="D118" t="str">
         <v>KROM</v>
@@ -3290,7 +3290,7 @@
         <v>Viktor Nyström</v>
       </c>
       <c r="C119" t="str">
-        <v>940724-1349</v>
+        <v>940724-9821</v>
       </c>
       <c r="D119" t="str">
         <v>ROM2</v>
@@ -3313,7 +3313,7 @@
         <v>Daniel Larsson</v>
       </c>
       <c r="C120" t="str">
-        <v>980123-3546</v>
+        <v>980123-9873</v>
       </c>
       <c r="D120" t="str">
         <v>Stöd och matchning</v>
@@ -3371,7 +3371,7 @@
         <v>Ibrahim Bengtsson</v>
       </c>
       <c r="C122" t="str">
-        <v>960707-0795</v>
+        <v>960707-9812</v>
       </c>
       <c r="D122" t="str">
         <v>KROM</v>
@@ -3394,7 +3394,7 @@
         <v>Omar Wallin</v>
       </c>
       <c r="C123" t="str">
-        <v>750508-3555</v>
+        <v>750508-9875</v>
       </c>
       <c r="D123" t="str">
         <v>Stöd och matchning</v>
@@ -3417,7 +3417,7 @@
         <v>Nadia Nordin</v>
       </c>
       <c r="C124" t="str">
-        <v>820414-3153</v>
+        <v>820414-9861</v>
       </c>
       <c r="D124" t="str">
         <v>Stöd och matchning</v>
@@ -3440,7 +3440,7 @@
         <v>Rania Söderberg</v>
       </c>
       <c r="C125" t="str">
-        <v>780613-8009</v>
+        <v>780613-9965</v>
       </c>
       <c r="D125" t="str">
         <v>KROM</v>
@@ -3460,7 +3460,7 @@
         <v>Hassan Bergström</v>
       </c>
       <c r="C126" t="str">
-        <v>751008-5454</v>
+        <v>751008-9902</v>
       </c>
       <c r="D126" t="str">
         <v>KVL</v>
@@ -3489,7 +3489,7 @@
         <v>Saga Engström</v>
       </c>
       <c r="C127" t="str">
-        <v>880115-8448</v>
+        <v>880115-9966</v>
       </c>
       <c r="D127" t="str">
         <v>ROM2</v>
@@ -3509,7 +3509,7 @@
         <v>Erik Magnusson</v>
       </c>
       <c r="C128" t="str">
-        <v>710831-0686</v>
+        <v>710831-9810</v>
       </c>
       <c r="D128" t="str">
         <v>ROM2</v>
@@ -3538,7 +3538,7 @@
         <v>Agnes Ali</v>
       </c>
       <c r="C129" t="str">
-        <v>660402-5921</v>
+        <v>660402-9915</v>
       </c>
       <c r="D129" t="str">
         <v>ROM2</v>
@@ -3567,7 +3567,7 @@
         <v>Arvid Persson</v>
       </c>
       <c r="C130" t="str">
-        <v>050809-9090</v>
+        <v>050809-9983</v>
       </c>
       <c r="D130" t="str">
         <v>Stöd och matchning</v>
@@ -3590,7 +3590,7 @@
         <v>Omar Berg</v>
       </c>
       <c r="C131" t="str">
-        <v>721110-5049</v>
+        <v>721110-9900</v>
       </c>
       <c r="D131" t="str">
         <v>Stöd och matchning</v>
@@ -3619,7 +3619,7 @@
         <v>Omar Jansson</v>
       </c>
       <c r="C132" t="str">
-        <v>021206-7599</v>
+        <v>021206-9959</v>
       </c>
       <c r="D132" t="str">
         <v>ROM2</v>
@@ -3642,7 +3642,7 @@
         <v>Kerim Mohamed</v>
       </c>
       <c r="C133" t="str">
-        <v>040110-3387</v>
+        <v>040110-9863</v>
       </c>
       <c r="D133" t="str">
         <v>KROM</v>
@@ -3665,7 +3665,7 @@
         <v>Elin Mohamed</v>
       </c>
       <c r="C134" t="str">
-        <v>960607-7361</v>
+        <v>960607-9946</v>
       </c>
       <c r="D134" t="str">
         <v>KROM</v>
@@ -3688,7 +3688,7 @@
         <v>Agnes Lindberg</v>
       </c>
       <c r="C135" t="str">
-        <v>781017-2010</v>
+        <v>781017-9841</v>
       </c>
       <c r="D135" t="str">
         <v>Stöd och matchning</v>
@@ -3717,7 +3717,7 @@
         <v>Johan Olsson</v>
       </c>
       <c r="C136" t="str">
-        <v>990213-8529</v>
+        <v>990213-9972</v>
       </c>
       <c r="D136" t="str">
         <v>Stöd och matchning</v>
@@ -3746,7 +3746,7 @@
         <v>Hugo Engström</v>
       </c>
       <c r="C137" t="str">
-        <v>811117-2634</v>
+        <v>811117-9852</v>
       </c>
       <c r="D137" t="str">
         <v>Stöd och matchning</v>
@@ -3775,7 +3775,7 @@
         <v>Karl Mohamed</v>
       </c>
       <c r="C138" t="str">
-        <v>890213-9610</v>
+        <v>890213-9990</v>
       </c>
       <c r="D138" t="str">
         <v>ROM2</v>
@@ -3795,7 +3795,7 @@
         <v>Jakob Pettersson</v>
       </c>
       <c r="C139" t="str">
-        <v>800513-3627</v>
+        <v>800513-9871</v>
       </c>
       <c r="D139" t="str">
         <v>Stöd och matchning</v>
@@ -3824,7 +3824,7 @@
         <v>Aisha Åberg</v>
       </c>
       <c r="C140" t="str">
-        <v>711220-4115</v>
+        <v>711220-9882</v>
       </c>
       <c r="D140" t="str">
         <v>Stöd och matchning</v>
@@ -3844,7 +3844,7 @@
         <v>Fatima Lindberg</v>
       </c>
       <c r="C141" t="str">
-        <v>930621-8448</v>
+        <v>930621-9966</v>
       </c>
       <c r="D141" t="str">
         <v>Stöd och matchning</v>
@@ -3864,7 +3864,7 @@
         <v>Ahmed Magnusson</v>
       </c>
       <c r="C142" t="str">
-        <v>010704-5130</v>
+        <v>010704-9900</v>
       </c>
       <c r="D142" t="str">
         <v>Stöd och matchning</v>
@@ -3893,7 +3893,7 @@
         <v>Selma Öberg</v>
       </c>
       <c r="C143" t="str">
-        <v>750831-7281</v>
+        <v>750831-9949</v>
       </c>
       <c r="D143" t="str">
         <v>KROM</v>
@@ -3922,7 +3922,7 @@
         <v>Hassan Yilmaz</v>
       </c>
       <c r="C144" t="str">
-        <v>850326-2886</v>
+        <v>850326-9857</v>
       </c>
       <c r="D144" t="str">
         <v>KROM</v>
@@ -3945,7 +3945,7 @@
         <v>Axel Sjöberg</v>
       </c>
       <c r="C145" t="str">
-        <v>740802-8053</v>
+        <v>740802-9960</v>
       </c>
       <c r="D145" t="str">
         <v>Stöd och matchning</v>
@@ -3974,7 +3974,7 @@
         <v>Leila Olsson</v>
       </c>
       <c r="C146" t="str">
-        <v>020530-4892</v>
+        <v>020530-9891</v>
       </c>
       <c r="D146" t="str">
         <v>ROM2</v>
@@ -3997,7 +3997,7 @@
         <v>Nadia Svensson</v>
       </c>
       <c r="C147" t="str">
-        <v>000228-0337</v>
+        <v>000228-9809</v>
       </c>
       <c r="D147" t="str">
         <v>KROM</v>
@@ -4020,7 +4020,7 @@
         <v>Ibrahim Pettersson</v>
       </c>
       <c r="C148" t="str">
-        <v>880505-6200</v>
+        <v>880505-9923</v>
       </c>
       <c r="D148" t="str">
         <v>KROM</v>
@@ -4043,7 +4043,7 @@
         <v>Elin Hassan</v>
       </c>
       <c r="C149" t="str">
-        <v>730303-5369</v>
+        <v>730303-9908</v>
       </c>
       <c r="D149" t="str">
         <v>ROM2</v>
@@ -4072,7 +4072,7 @@
         <v>Karl Bengtsson</v>
       </c>
       <c r="C150" t="str">
-        <v>820625-5633</v>
+        <v>820625-9916</v>
       </c>
       <c r="D150" t="str">
         <v>KROM</v>
@@ -4101,7 +4101,7 @@
         <v>Elias Larsson</v>
       </c>
       <c r="C151" t="str">
-        <v>040423-9790</v>
+        <v>040423-9998</v>
       </c>
       <c r="D151" t="str">
         <v>KROM</v>
@@ -4124,7 +4124,7 @@
         <v>Ibrahim Olsson</v>
       </c>
       <c r="C152" t="str">
-        <v>700613-1408</v>
+        <v>700613-9823</v>
       </c>
       <c r="D152" t="str">
         <v>KROM</v>
@@ -4147,7 +4147,7 @@
         <v>Axel Jonsson</v>
       </c>
       <c r="C153" t="str">
-        <v>670420-9516</v>
+        <v>670420-9995</v>
       </c>
       <c r="D153" t="str">
         <v>ROM2</v>
@@ -4167,7 +4167,7 @@
         <v>Linnea Jakobsson</v>
       </c>
       <c r="C154" t="str">
-        <v>970119-5068</v>
+        <v>970119-9904</v>
       </c>
       <c r="D154" t="str">
         <v>Stöd och matchning</v>
@@ -4196,7 +4196,7 @@
         <v>Abdi Holm</v>
       </c>
       <c r="C155" t="str">
-        <v>970731-4143</v>
+        <v>970731-9886</v>
       </c>
       <c r="D155" t="str">
         <v>Stöd och matchning</v>
@@ -4216,7 +4216,7 @@
         <v>Ibrahim Forsberg</v>
       </c>
       <c r="C156" t="str">
-        <v>820124-9672</v>
+        <v>820124-9995</v>
       </c>
       <c r="D156" t="str">
         <v>KVL</v>
@@ -4245,7 +4245,7 @@
         <v>Johan Forsberg</v>
       </c>
       <c r="C157" t="str">
-        <v>780130-7666</v>
+        <v>780130-9951</v>
       </c>
       <c r="D157" t="str">
         <v>Stöd och matchning</v>
@@ -4268,7 +4268,7 @@
         <v>Nadia Nilsson</v>
       </c>
       <c r="C158" t="str">
-        <v>620514-9773</v>
+        <v>620514-9997</v>
       </c>
       <c r="D158" t="str">
         <v>Stöd och matchning</v>
@@ -4297,7 +4297,7 @@
         <v>Rania Bengtsson</v>
       </c>
       <c r="C159" t="str">
-        <v>010614-9701</v>
+        <v>010614-9990</v>
       </c>
       <c r="D159" t="str">
         <v>ROM2</v>
@@ -4320,7 +4320,7 @@
         <v>Erik Persson</v>
       </c>
       <c r="C160" t="str">
-        <v>980420-3363</v>
+        <v>980420-9865</v>
       </c>
       <c r="D160" t="str">
         <v>Stöd och matchning</v>
@@ -4343,7 +4343,7 @@
         <v>Ebba Engström</v>
       </c>
       <c r="C161" t="str">
-        <v>700205-8373</v>
+        <v>700205-9967</v>
       </c>
       <c r="D161" t="str">
         <v>Stöd och matchning</v>
@@ -4372,7 +4372,7 @@
         <v>Daniel Wallin</v>
       </c>
       <c r="C162" t="str">
-        <v>841127-4585</v>
+        <v>841127-9899</v>
       </c>
       <c r="D162" t="str">
         <v>KROM</v>
@@ -4395,7 +4395,7 @@
         <v>Ebba Olsson</v>
       </c>
       <c r="C163" t="str">
-        <v>910809-9780</v>
+        <v>910809-9996</v>
       </c>
       <c r="D163" t="str">
         <v>KROM</v>
@@ -4421,7 +4421,7 @@
         <v>Sara Sjöberg</v>
       </c>
       <c r="C164" t="str">
-        <v>680804-9131</v>
+        <v>680804-9982</v>
       </c>
       <c r="D164" t="str">
         <v>Stöd och matchning</v>
@@ -4450,7 +4450,7 @@
         <v>Klara Sandberg</v>
       </c>
       <c r="C165" t="str">
-        <v>871113-4844</v>
+        <v>871113-9892</v>
       </c>
       <c r="D165" t="str">
         <v>ROM2</v>
@@ -4479,7 +4479,7 @@
         <v>Rania Ahmed</v>
       </c>
       <c r="C166" t="str">
-        <v>690501-4327</v>
+        <v>690501-9888</v>
       </c>
       <c r="D166" t="str">
         <v>KROM</v>
@@ -4502,7 +4502,7 @@
         <v>Vera Nyström</v>
       </c>
       <c r="C167" t="str">
-        <v>810901-8351</v>
+        <v>810901-9961</v>
       </c>
       <c r="D167" t="str">
         <v>KVL</v>
@@ -4531,7 +4531,7 @@
         <v>Yusuf Ström</v>
       </c>
       <c r="C168" t="str">
-        <v>740723-1583</v>
+        <v>740723-9834</v>
       </c>
       <c r="D168" t="str">
         <v>Stöd och matchning</v>
@@ -4560,7 +4560,7 @@
         <v>Gustav Bengtsson</v>
       </c>
       <c r="C169" t="str">
-        <v>051204-8513</v>
+        <v>051204-9974</v>
       </c>
       <c r="D169" t="str">
         <v>KVL</v>
@@ -4589,7 +4589,7 @@
         <v>Dalia Sjöberg</v>
       </c>
       <c r="C170" t="str">
-        <v>980110-0745</v>
+        <v>980110-9811</v>
       </c>
       <c r="D170" t="str">
         <v>KROM</v>
@@ -4609,7 +4609,7 @@
         <v>Yusuf Yilmaz</v>
       </c>
       <c r="C171" t="str">
-        <v>740223-7577</v>
+        <v>740223-9953</v>
       </c>
       <c r="D171" t="str">
         <v>Stöd och matchning</v>
@@ -4638,7 +4638,7 @@
         <v>Yasmin Söderberg</v>
       </c>
       <c r="C172" t="str">
-        <v>650310-0015</v>
+        <v>650310-9800</v>
       </c>
       <c r="D172" t="str">
         <v>Stöd och matchning</v>
@@ -4667,7 +4667,7 @@
         <v>Kerim Ahmed</v>
       </c>
       <c r="C173" t="str">
-        <v>011022-8863</v>
+        <v>011022-9978</v>
       </c>
       <c r="D173" t="str">
         <v>KROM</v>
@@ -4690,7 +4690,7 @@
         <v>Jakob Sjöberg</v>
       </c>
       <c r="C174" t="str">
-        <v>770304-4151</v>
+        <v>770304-9887</v>
       </c>
       <c r="D174" t="str">
         <v>Stöd och matchning</v>
@@ -4719,7 +4719,7 @@
         <v>Emil Öberg</v>
       </c>
       <c r="C175" t="str">
-        <v>701202-7947</v>
+        <v>701202-9950</v>
       </c>
       <c r="D175" t="str">
         <v>Stöd och matchning</v>
@@ -4742,7 +4742,7 @@
         <v>Johan Eriksson</v>
       </c>
       <c r="C176" t="str">
-        <v>980429-5369</v>
+        <v>980429-9908</v>
       </c>
       <c r="D176" t="str">
         <v>ROM2</v>
@@ -4771,7 +4771,7 @@
         <v>Yusuf Bergström</v>
       </c>
       <c r="C177" t="str">
-        <v>920504-6270</v>
+        <v>920504-9928</v>
       </c>
       <c r="D177" t="str">
         <v>Stöd och matchning</v>
@@ -4800,7 +4800,7 @@
         <v>Ebba Danielsson</v>
       </c>
       <c r="C178" t="str">
-        <v>780807-3253</v>
+        <v>780807-9862</v>
       </c>
       <c r="D178" t="str">
         <v>KVL</v>
@@ -4829,7 +4829,7 @@
         <v>Gustav Hansson</v>
       </c>
       <c r="C179" t="str">
-        <v>020215-0942</v>
+        <v>020215-9810</v>
       </c>
       <c r="D179" t="str">
         <v>Stöd och matchning</v>
@@ -4858,7 +4858,7 @@
         <v>Leila Axelsson</v>
       </c>
       <c r="C180" t="str">
-        <v>701019-4863</v>
+        <v>701019-9896</v>
       </c>
       <c r="D180" t="str">
         <v>ROM2</v>
@@ -4881,7 +4881,7 @@
         <v>Zainab Ali</v>
       </c>
       <c r="C181" t="str">
-        <v>841130-5298</v>
+        <v>841130-9902</v>
       </c>
       <c r="D181" t="str">
         <v>KVL</v>
@@ -4904,7 +4904,7 @@
         <v>Klara Eklund</v>
       </c>
       <c r="C182" t="str">
-        <v>680214-9069</v>
+        <v>680214-9986</v>
       </c>
       <c r="D182" t="str">
         <v>KVL</v>
@@ -4927,7 +4927,7 @@
         <v>Linnea Pettersson</v>
       </c>
       <c r="C183" t="str">
-        <v>871223-6044</v>
+        <v>871223-9923</v>
       </c>
       <c r="D183" t="str">
         <v>KVL</v>
@@ -4950,7 +4950,7 @@
         <v>Kerim Lindström</v>
       </c>
       <c r="C184" t="str">
-        <v>760706-3000</v>
+        <v>760706-9866</v>
       </c>
       <c r="D184" t="str">
         <v>KROM</v>
@@ -4970,7 +4970,7 @@
         <v>Sofia Magnusson</v>
       </c>
       <c r="C185" t="str">
-        <v>891012-7060</v>
+        <v>891012-9942</v>
       </c>
       <c r="D185" t="str">
         <v>ROM2</v>
@@ -4999,7 +4999,7 @@
         <v>Nadia Ahmed</v>
       </c>
       <c r="C186" t="str">
-        <v>890120-0082</v>
+        <v>890120-9802</v>
       </c>
       <c r="D186" t="str">
         <v>KROM</v>
@@ -5019,7 +5019,7 @@
         <v>Fatima Berg</v>
       </c>
       <c r="C187" t="str">
-        <v>890430-9336</v>
+        <v>890430-9989</v>
       </c>
       <c r="D187" t="str">
         <v>Stöd och matchning</v>
@@ -5039,7 +5039,7 @@
         <v>Abdi Lindberg</v>
       </c>
       <c r="C188" t="str">
-        <v>980701-3066</v>
+        <v>980701-9865</v>
       </c>
       <c r="D188" t="str">
         <v>ROM2</v>
@@ -5059,7 +5059,7 @@
         <v>Rania Eriksson</v>
       </c>
       <c r="C189" t="str">
-        <v>960323-6614</v>
+        <v>960323-9931</v>
       </c>
       <c r="D189" t="str">
         <v>KROM</v>
@@ -5088,7 +5088,7 @@
         <v>Lucas Axelsson</v>
       </c>
       <c r="C190" t="str">
-        <v>721025-1836</v>
+        <v>721025-9839</v>
       </c>
       <c r="D190" t="str">
         <v>ROM2</v>
@@ -5111,7 +5111,7 @@
         <v>Sofia Nilsson</v>
       </c>
       <c r="C191" t="str">
-        <v>010125-1361</v>
+        <v>010125-9828</v>
       </c>
       <c r="D191" t="str">
         <v>ROM2</v>
@@ -5131,7 +5131,7 @@
         <v>Mohammed Söderberg</v>
       </c>
       <c r="C192" t="str">
-        <v>631013-4918</v>
+        <v>631013-9891</v>
       </c>
       <c r="D192" t="str">
         <v>KROM</v>
@@ -5160,7 +5160,7 @@
         <v>Ludvig Demir</v>
       </c>
       <c r="C193" t="str">
-        <v>931021-6198</v>
+        <v>931021-9929</v>
       </c>
       <c r="D193" t="str">
         <v>Stöd och matchning</v>
@@ -5180,7 +5180,7 @@
         <v>Aisha Axelsson</v>
       </c>
       <c r="C194" t="str">
-        <v>860324-0212</v>
+        <v>860324-9809</v>
       </c>
       <c r="D194" t="str">
         <v>ROM2</v>
@@ -5209,7 +5209,7 @@
         <v>Anna Axelsson</v>
       </c>
       <c r="C195" t="str">
-        <v>020401-5234</v>
+        <v>020401-9905</v>
       </c>
       <c r="D195" t="str">
         <v>ROM2</v>
@@ -5229,7 +5229,7 @@
         <v>Hassan Pettersson</v>
       </c>
       <c r="C196" t="str">
-        <v>801215-6827</v>
+        <v>801215-9938</v>
       </c>
       <c r="D196" t="str">
         <v>KROM</v>
@@ -5252,7 +5252,7 @@
         <v>Johan Engström</v>
       </c>
       <c r="C197" t="str">
-        <v>861230-9545</v>
+        <v>861230-9990</v>
       </c>
       <c r="D197" t="str">
         <v>Stöd och matchning</v>
@@ -5281,7 +5281,7 @@
         <v>Maja Sjöberg</v>
       </c>
       <c r="C198" t="str">
-        <v>781218-6901</v>
+        <v>781218-9939</v>
       </c>
       <c r="D198" t="str">
         <v>KVL</v>
@@ -5310,7 +5310,7 @@
         <v>Mariam Ahmed</v>
       </c>
       <c r="C199" t="str">
-        <v>800212-3993</v>
+        <v>800212-9875</v>
       </c>
       <c r="D199" t="str">
         <v>KVL</v>
@@ -5333,7 +5333,7 @@
         <v>Samir Jansson</v>
       </c>
       <c r="C200" t="str">
-        <v>010526-9500</v>
+        <v>010526-9989</v>
       </c>
       <c r="D200" t="str">
         <v>ROM2</v>
@@ -5359,7 +5359,7 @@
         <v>Sofia Lindberg</v>
       </c>
       <c r="C201" t="str">
-        <v>010906-2364</v>
+        <v>010906-9849</v>
       </c>
       <c r="D201" t="str">
         <v>Stöd och matchning</v>
@@ -5388,7 +5388,7 @@
         <v>Aisha Gustafsson</v>
       </c>
       <c r="C202" t="str">
-        <v>710319-7542</v>
+        <v>710319-9951</v>
       </c>
       <c r="D202" t="str">
         <v>Stöd och matchning</v>
@@ -5417,7 +5417,7 @@
         <v>Maja Ahmed</v>
       </c>
       <c r="C203" t="str">
-        <v>661127-1914</v>
+        <v>661127-9834</v>
       </c>
       <c r="D203" t="str">
         <v>KVL</v>
@@ -5440,7 +5440,7 @@
         <v>Yusuf Kaya</v>
       </c>
       <c r="C204" t="str">
-        <v>871017-9758</v>
+        <v>871017-9998</v>
       </c>
       <c r="D204" t="str">
         <v>ROM2</v>
@@ -5460,7 +5460,7 @@
         <v>Emil Eklund</v>
       </c>
       <c r="C205" t="str">
-        <v>790726-3623</v>
+        <v>790726-9877</v>
       </c>
       <c r="D205" t="str">
         <v>Stöd och matchning</v>
